--- a/TP 2/TP2_G2_DIOP_Mareme_KANE_Boubacar/outputs/tableaux_TP2.xlsx
+++ b/TP 2/TP2_G2_DIOP_Mareme_KANE_Boubacar/outputs/tableaux_TP2.xlsx
@@ -15,17 +15,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t xml:space="preserve">niveau_educ</t>
   </si>
   <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
     <t xml:space="preserve">pct</t>
   </si>
   <si>
+    <t xml:space="preserve">ic_bas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ic_haut</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aucun</t>
   </si>
   <si>
@@ -44,6 +47,21 @@
     <t xml:space="preserve">sexe</t>
   </si>
   <si>
+    <t xml:space="preserve">se.niveau_educAucun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se.niveau_educPrimaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se.niveau_educJunior Secondary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se.niveau_educSenior Secondary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se.niveau_educTertiaire</t>
+  </si>
+  <si>
     <t xml:space="preserve">Homme</t>
   </si>
   <si>
@@ -53,30 +71,33 @@
     <t xml:space="preserve">milieu</t>
   </si>
   <si>
-    <t xml:space="preserve">scolarise</t>
+    <t xml:space="preserve">scolariseScolarisé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scolariseNon scolarisé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ci_l.scolariseScolarisé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ci_l.scolariseNon scolarisé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ci_u.scolariseScolarisé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ci_u.scolariseNon scolarisé</t>
   </si>
   <si>
     <t xml:space="preserve">Urbain</t>
   </si>
   <si>
-    <t xml:space="preserve">Scolarisé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non scolarisé</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rural</t>
   </si>
   <si>
     <t xml:space="preserve">state</t>
   </si>
   <si>
-    <t xml:space="preserve">n_total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_analph</t>
-  </si>
-  <si>
     <t xml:space="preserve">taux_analph</t>
   </si>
   <si>
@@ -95,40 +116,46 @@
     <t xml:space="preserve">5. Bauchi</t>
   </si>
   <si>
+    <t xml:space="preserve">22. Kogi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23. Kwara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34. Taraba</t>
+  </si>
+  <si>
     <t xml:space="preserve">31. Plateau</t>
   </si>
   <si>
-    <t xml:space="preserve">22. Kogi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34. Taraba</t>
+    <t xml:space="preserve">2. Adamawa</t>
   </si>
   <si>
     <t xml:space="preserve">35. Yobe</t>
   </si>
   <si>
+    <t xml:space="preserve">9. Cross River</t>
+  </si>
+  <si>
     <t xml:space="preserve">20. Katsina</t>
   </si>
   <si>
-    <t xml:space="preserve">23. Kwara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Adamawa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. Cross River</t>
+    <t xml:space="preserve">15. Gombe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14. Enugu</t>
   </si>
   <si>
     <t xml:space="preserve">18. Kaduna</t>
   </si>
   <si>
+    <t xml:space="preserve">30. Oyo</t>
+  </si>
+  <si>
     <t xml:space="preserve">7. Benue</t>
   </si>
   <si>
-    <t xml:space="preserve">30. Oyo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14. Enugu</t>
+    <t xml:space="preserve">29. Osun</t>
   </si>
   <si>
     <t xml:space="preserve">28. Ondo</t>
@@ -137,58 +164,52 @@
     <t xml:space="preserve">11. Ebonyi</t>
   </si>
   <si>
-    <t xml:space="preserve">15. Gombe</t>
+    <t xml:space="preserve">19. Kano</t>
   </si>
   <si>
     <t xml:space="preserve">33. Sokoto</t>
   </si>
   <si>
-    <t xml:space="preserve">29. Osun</t>
-  </si>
-  <si>
     <t xml:space="preserve">6. Bayelsa</t>
   </si>
   <si>
     <t xml:space="preserve">4. Anambra</t>
   </si>
   <si>
-    <t xml:space="preserve">19. Kano</t>
+    <t xml:space="preserve">25. Nasarawa</t>
   </si>
   <si>
     <t xml:space="preserve">12. Edo</t>
   </si>
   <si>
+    <t xml:space="preserve">27. Ogun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36. Zamfara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Delta</t>
+  </si>
+  <si>
     <t xml:space="preserve">17. Jigawa</t>
   </si>
   <si>
+    <t xml:space="preserve">16. Imo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Akwa Ibom</t>
+  </si>
+  <si>
     <t xml:space="preserve">37. FCT</t>
   </si>
   <si>
-    <t xml:space="preserve">10. Delta</t>
-  </si>
-  <si>
     <t xml:space="preserve">13. Ekiti</t>
   </si>
   <si>
-    <t xml:space="preserve">25. Nasarawa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27. Ogun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16. Imo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36. Zamfara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Akwa Ibom</t>
+    <t xml:space="preserve">32. Rivers</t>
   </si>
   <si>
     <t xml:space="preserve">1. Abia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32. Rivers</t>
   </si>
   <si>
     <t xml:space="preserve">24. Lagos</t>
@@ -530,60 +551,78 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>6155</v>
+        <v>25.9655785182665</v>
       </c>
       <c r="C2" t="n">
-        <v>26.1</v>
+        <v>24.7350591032223</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.1960979333107</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>7068</v>
+        <v>29.7405775690397</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>28.7472706645609</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30.7338844735185</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>2129</v>
+        <v>8.78626511570654</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>8.23572428957826</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.33680594183482</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>4663</v>
+        <v>18.9975513978839</v>
       </c>
       <c r="C5" t="n">
-        <v>19.8</v>
+        <v>18.0785554984662</v>
+      </c>
+      <c r="D5" t="n">
+        <v>19.9165472973016</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>3549</v>
+        <v>16.5100273991034</v>
       </c>
       <c r="C6" t="n">
-        <v>15.1</v>
+        <v>15.3171751624275</v>
+      </c>
+      <c r="D6" t="n">
+        <v>17.7028796357793</v>
       </c>
     </row>
   </sheetData>
@@ -599,156 +638,288 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+        <v>15</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.00638193516202825</v>
       </c>
       <c r="C2" t="n">
-        <v>926</v>
+        <v>0.00702600543657981</v>
       </c>
       <c r="D2" t="n">
-        <v>14.6</v>
+        <v>0.00402036982456521</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.00928629631871268</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.00941740857091551</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>14.2657002298713</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.00638193516202825</v>
       </c>
       <c r="C3" t="n">
-        <v>1198</v>
+        <v>0.00702600543657981</v>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>0.00402036982456521</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00928629631871268</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.00941740857091551</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>18.9829566257862</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.00638193516202825</v>
       </c>
       <c r="C4" t="n">
-        <v>359</v>
+        <v>0.00702600543657981</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7</v>
+        <v>0.00402036982456521</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.00928629631871268</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.00941740857091551</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.49187258409846</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
+        <v>15</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.00638193516202825</v>
       </c>
       <c r="C5" t="n">
-        <v>2185</v>
+        <v>0.00702600543657981</v>
       </c>
       <c r="D5" t="n">
-        <v>34.5</v>
+        <v>0.00402036982456521</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.00928629631871268</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.00941740857091551</v>
+      </c>
+      <c r="G5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>33.5585216365012</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.00638193516202825</v>
       </c>
       <c r="C6" t="n">
-        <v>1663</v>
+        <v>0.00702600543657981</v>
       </c>
       <c r="D6" t="n">
-        <v>26.3</v>
+        <v>0.00402036982456521</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.00928629631871268</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.00941740857091551</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>27.7009489237428</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
+        <v>16</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.00876789973166397</v>
       </c>
       <c r="C7" t="n">
-        <v>2194</v>
+        <v>0.00664888416866028</v>
       </c>
       <c r="D7" t="n">
-        <v>31.1</v>
+        <v>0.00408626275601002</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.00780709730433377</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.00882929044037542</v>
+      </c>
+      <c r="G7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>29.972118101581</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.00876789973166397</v>
       </c>
       <c r="C8" t="n">
-        <v>1416</v>
+        <v>0.00664888416866028</v>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>0.00408626275601002</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.00780709730433377</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.00882929044037542</v>
+      </c>
+      <c r="G8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>19.6750742503623</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.00876789973166397</v>
       </c>
       <c r="C9" t="n">
-        <v>379</v>
+        <v>0.00664888416866028</v>
       </c>
       <c r="D9" t="n">
-        <v>5.4</v>
+        <v>0.00408626275601002</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.00780709730433377</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.00882929044037542</v>
+      </c>
+      <c r="G9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.64760663595268</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>6</v>
+        <v>16</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.00876789973166397</v>
       </c>
       <c r="C10" t="n">
-        <v>1706</v>
+        <v>0.00664888416866028</v>
       </c>
       <c r="D10" t="n">
-        <v>24.2</v>
+        <v>0.00408626275601002</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.00780709730433377</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.00882929044037542</v>
+      </c>
+      <c r="G10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23.4933112106082</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>7</v>
+        <v>16</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.00876789973166397</v>
       </c>
       <c r="C11" t="n">
-        <v>1366</v>
+        <v>0.00664888416866028</v>
       </c>
       <c r="D11" t="n">
-        <v>19.3</v>
+        <v>0.00408626275601002</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.00780709730433377</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.00882929044037542</v>
+      </c>
+      <c r="G11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>21.2118898014958</v>
       </c>
     </row>
   </sheetData>
@@ -764,72 +935,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>2</v>
+      </c>
+      <c r="J1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.882082690026847</v>
       </c>
       <c r="C2" t="n">
-        <v>2136</v>
+        <v>0.117917309973153</v>
       </c>
       <c r="D2" t="n">
-        <v>88.5</v>
+        <v>0.859181862583639</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0950164825299462</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.904983517470054</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.140818137416361</v>
+      </c>
+      <c r="H2" t="n">
+        <v>88.2082690026847</v>
+      </c>
+      <c r="I2" t="n">
+        <v>85.9181862583639</v>
+      </c>
+      <c r="J2" t="n">
+        <v>90.4983517470054</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
+        <v>25</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.732846060557921</v>
       </c>
       <c r="C3" t="n">
-        <v>277</v>
+        <v>0.267153939442079</v>
       </c>
       <c r="D3" t="n">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4880</v>
-      </c>
-      <c r="D4" t="n">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1847</v>
-      </c>
-      <c r="D5" t="n">
-        <v>27.5</v>
+        <v>0.711109199295301</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.245417078179458</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.754582921820542</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.288890800704699</v>
+      </c>
+      <c r="H3" t="n">
+        <v>73.2846060557921</v>
+      </c>
+      <c r="I3" t="n">
+        <v>71.1109199295301</v>
+      </c>
+      <c r="J3" t="n">
+        <v>75.4582921820542</v>
       </c>
     </row>
   </sheetData>
@@ -845,647 +1042,419 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B2" t="n">
-        <v>239</v>
+        <v>72.5118486756045</v>
       </c>
       <c r="C2" t="n">
-        <v>165</v>
-      </c>
-      <c r="D2" t="n">
-        <v>69.0376569037657</v>
-      </c>
-      <c r="E2" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B3" t="n">
-        <v>378</v>
+        <v>60.4302484059137</v>
       </c>
       <c r="C3" t="n">
-        <v>210</v>
-      </c>
-      <c r="D3" t="n">
-        <v>55.5555555555556</v>
-      </c>
-      <c r="E3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B4" t="n">
-        <v>142</v>
+        <v>55.276028630914</v>
       </c>
       <c r="C4" t="n">
-        <v>76</v>
-      </c>
-      <c r="D4" t="n">
-        <v>53.5211267605634</v>
-      </c>
-      <c r="E4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B5" t="n">
-        <v>694</v>
+        <v>50.8840325622702</v>
       </c>
       <c r="C5" t="n">
-        <v>339</v>
-      </c>
-      <c r="D5" t="n">
-        <v>48.8472622478386</v>
-      </c>
-      <c r="E5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B6" t="n">
-        <v>264</v>
+        <v>42.9761609504494</v>
       </c>
       <c r="C6" t="n">
-        <v>123</v>
-      </c>
-      <c r="D6" t="n">
-        <v>46.5909090909091</v>
-      </c>
-      <c r="E6" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B7" t="n">
-        <v>271</v>
+        <v>39.65972276604</v>
       </c>
       <c r="C7" t="n">
-        <v>115</v>
-      </c>
-      <c r="D7" t="n">
-        <v>42.4354243542435</v>
-      </c>
-      <c r="E7" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B8" t="n">
-        <v>354</v>
+        <v>39.4505025281762</v>
       </c>
       <c r="C8" t="n">
-        <v>149</v>
-      </c>
-      <c r="D8" t="n">
-        <v>42.090395480226</v>
-      </c>
-      <c r="E8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B9" t="n">
-        <v>206</v>
+        <v>38.5112809465484</v>
       </c>
       <c r="C9" t="n">
-        <v>84</v>
-      </c>
-      <c r="D9" t="n">
-        <v>40.7766990291262</v>
-      </c>
-      <c r="E9" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B10" t="n">
-        <v>485</v>
+        <v>37.4376376531348</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
-      </c>
-      <c r="D10" t="n">
-        <v>35.8762886597938</v>
-      </c>
-      <c r="E10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B11" t="n">
-        <v>455</v>
+        <v>36.9278891646633</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
-      </c>
-      <c r="D11" t="n">
-        <v>35.8241758241758</v>
-      </c>
-      <c r="E11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>743</v>
+        <v>33.4872616203106</v>
       </c>
       <c r="C12" t="n">
-        <v>263</v>
-      </c>
-      <c r="D12" t="n">
-        <v>35.3970390309556</v>
-      </c>
-      <c r="E12" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>224</v>
+        <v>32.2817738479132</v>
       </c>
       <c r="C13" t="n">
-        <v>77</v>
-      </c>
-      <c r="D13" t="n">
-        <v>34.375</v>
-      </c>
-      <c r="E13" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B14" t="n">
-        <v>672</v>
+        <v>31.2822962830487</v>
       </c>
       <c r="C14" t="n">
-        <v>208</v>
-      </c>
-      <c r="D14" t="n">
-        <v>30.952380952381</v>
-      </c>
-      <c r="E14" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B15" t="n">
-        <v>471</v>
+        <v>29.1166633687737</v>
       </c>
       <c r="C15" t="n">
-        <v>142</v>
-      </c>
-      <c r="D15" t="n">
-        <v>30.1486199575372</v>
-      </c>
-      <c r="E15" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B16" t="n">
-        <v>277</v>
+        <v>28.7123835419442</v>
       </c>
       <c r="C16" t="n">
-        <v>83</v>
-      </c>
-      <c r="D16" t="n">
-        <v>29.9638989169675</v>
-      </c>
-      <c r="E16" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B17" t="n">
-        <v>377</v>
+        <v>28.0682141884842</v>
       </c>
       <c r="C17" t="n">
-        <v>112</v>
-      </c>
-      <c r="D17" t="n">
-        <v>29.7082228116711</v>
-      </c>
-      <c r="E17" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B18" t="n">
-        <v>182</v>
+        <v>27.9827995048737</v>
       </c>
       <c r="C18" t="n">
-        <v>48</v>
-      </c>
-      <c r="D18" t="n">
-        <v>26.3736263736264</v>
-      </c>
-      <c r="E18" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B19" t="n">
-        <v>333</v>
+        <v>25.6508192128017</v>
       </c>
       <c r="C19" t="n">
-        <v>86</v>
-      </c>
-      <c r="D19" t="n">
-        <v>25.8258258258258</v>
-      </c>
-      <c r="E19" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B20" t="n">
-        <v>475</v>
+        <v>24.7893604018565</v>
       </c>
       <c r="C20" t="n">
-        <v>122</v>
-      </c>
-      <c r="D20" t="n">
-        <v>25.6842105263158</v>
-      </c>
-      <c r="E20" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B21" t="n">
-        <v>188</v>
+        <v>24.4756582397606</v>
       </c>
       <c r="C21" t="n">
-        <v>46</v>
-      </c>
-      <c r="D21" t="n">
-        <v>24.468085106383</v>
-      </c>
-      <c r="E21" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B22" t="n">
-        <v>171</v>
+        <v>23.4834124719858</v>
       </c>
       <c r="C22" t="n">
-        <v>41</v>
-      </c>
-      <c r="D22" t="n">
-        <v>23.9766081871345</v>
-      </c>
-      <c r="E22" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B23" t="n">
-        <v>163</v>
+        <v>23.0350540757374</v>
       </c>
       <c r="C23" t="n">
-        <v>39</v>
-      </c>
-      <c r="D23" t="n">
-        <v>23.9263803680982</v>
-      </c>
-      <c r="E23" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B24" t="n">
-        <v>284</v>
+        <v>22.8755675159578</v>
       </c>
       <c r="C24" t="n">
-        <v>63</v>
-      </c>
-      <c r="D24" t="n">
-        <v>22.1830985915493</v>
-      </c>
-      <c r="E24" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B25" t="n">
-        <v>480</v>
+        <v>21.5148737285265</v>
       </c>
       <c r="C25" t="n">
-        <v>106</v>
-      </c>
-      <c r="D25" t="n">
-        <v>22.0833333333333</v>
-      </c>
-      <c r="E25" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B26" t="n">
-        <v>462</v>
+        <v>17.3199179238225</v>
       </c>
       <c r="C26" t="n">
-        <v>99</v>
-      </c>
-      <c r="D26" t="n">
-        <v>21.4285714285714</v>
-      </c>
-      <c r="E26" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B27" t="n">
-        <v>340</v>
+        <v>17.2773091217367</v>
       </c>
       <c r="C27" t="n">
-        <v>58</v>
-      </c>
-      <c r="D27" t="n">
-        <v>17.0588235294118</v>
-      </c>
-      <c r="E27" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B28" t="n">
-        <v>357</v>
+        <v>15.0438003587262</v>
       </c>
       <c r="C28" t="n">
-        <v>56</v>
-      </c>
-      <c r="D28" t="n">
-        <v>15.6862745098039</v>
-      </c>
-      <c r="E28" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B29" t="n">
-        <v>381</v>
+        <v>12.7708973571837</v>
       </c>
       <c r="C29" t="n">
-        <v>57</v>
-      </c>
-      <c r="D29" t="n">
-        <v>14.9606299212598</v>
-      </c>
-      <c r="E29" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B30" t="n">
-        <v>286</v>
+        <v>12.2974025294124</v>
       </c>
       <c r="C30" t="n">
-        <v>42</v>
-      </c>
-      <c r="D30" t="n">
-        <v>14.6853146853147</v>
-      </c>
-      <c r="E30" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B31" t="n">
-        <v>70</v>
+        <v>12.2627091960076</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
-      </c>
-      <c r="D31" t="n">
-        <v>14.2857142857143</v>
-      </c>
-      <c r="E31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B32" t="n">
-        <v>296</v>
+        <v>11.752164116617</v>
       </c>
       <c r="C32" t="n">
-        <v>42</v>
-      </c>
-      <c r="D32" t="n">
-        <v>14.1891891891892</v>
-      </c>
-      <c r="E32" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B33" t="n">
-        <v>403</v>
+        <v>11.47311695265</v>
       </c>
       <c r="C33" t="n">
-        <v>57</v>
-      </c>
-      <c r="D33" t="n">
-        <v>14.1439205955335</v>
-      </c>
-      <c r="E33" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B34" t="n">
-        <v>199</v>
+        <v>10.4068925029239</v>
       </c>
       <c r="C34" t="n">
-        <v>27</v>
-      </c>
-      <c r="D34" t="n">
-        <v>13.5678391959799</v>
-      </c>
-      <c r="E34" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B35" t="n">
-        <v>597</v>
+        <v>9.91556404026009</v>
       </c>
       <c r="C35" t="n">
-        <v>77</v>
-      </c>
-      <c r="D35" t="n">
-        <v>12.8978224455611</v>
-      </c>
-      <c r="E35" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B36" t="n">
-        <v>625</v>
+        <v>9.29602244935755</v>
       </c>
       <c r="C36" t="n">
-        <v>57</v>
-      </c>
-      <c r="D36" t="n">
-        <v>9.12</v>
-      </c>
-      <c r="E36" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B37" t="n">
-        <v>287</v>
+        <v>8.06418347942938</v>
       </c>
       <c r="C37" t="n">
-        <v>26</v>
-      </c>
-      <c r="D37" t="n">
-        <v>9.05923344947735</v>
-      </c>
-      <c r="E37" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B38" t="n">
-        <v>569</v>
+        <v>5.09852197797165</v>
       </c>
       <c r="C38" t="n">
-        <v>32</v>
-      </c>
-      <c r="D38" t="n">
-        <v>5.62390158172232</v>
-      </c>
-      <c r="E38" t="n">
         <v>1</v>
       </c>
     </row>
